--- a/outputs/2026-10-30-mcp-comparison/mcp-workflow-comparison.xlsx
+++ b/outputs/2026-10-30-mcp-comparison/mcp-workflow-comparison.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="1" r:id="R3b31e7c382bf43da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark" sheetId="2" r:id="Rbb7d01b3202042db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="1" r:id="R18bf33b258e04e43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark" sheetId="2" r:id="Rf8bbaeab469a4912"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,11 +14,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="200" formatCode="0.0"/>
     <x:numFmt numFmtId="201" formatCode="0.0%"/>
     <x:numFmt numFmtId="202" formatCode="0.00&quot;x&quot;"/>
     <x:numFmt numFmtId="203" formatCode="0"/>
+    <x:numFmt numFmtId="204" formatCode="0.00"/>
+    <x:numFmt numFmtId="205" formatCode="#,##0"/>
+    <x:numFmt numFmtId="206" formatCode="#,##0.0"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -61,7 +64,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -83,6 +86,26 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F3EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F3EA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF245942"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F3EA"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -96,7 +119,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="39">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -148,6 +171,58 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="206" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -364,6 +439,627 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/drawings/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>Mean scraper time (seconds), 10 runs each</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Prompt agent</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="83968B"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Comparison'!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Comparison'!$H$3</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Saved workflow</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="245942"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Comparison'!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Comparison'!$I$3</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>Observed field accuracy, 200 fields each</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Prompt agent</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="83968B"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Comparison'!$G$6</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Comparison'!$H$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Saved workflow</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="245942"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Comparison'!$G$6</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Comparison'!$I$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:rPr>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:rPr>
+              <a:t>Mean model tokens per run (includes cached input)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Prompt agent</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="83968B"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Comparison'!$G$40</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Comparison'!$H$40</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.0</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Saved workflow</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="245942"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Comparison'!$G$40</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Comparison'!$I$40</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.0</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900">
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="Arial"/>
+                <a:cs typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Arial"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
@@ -390,7 +1086,97 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R57efa2ec14e74888"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re271cd55082b4d50"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R469e483566d344be"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R04c43edd2c924cde"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R73cf55e225194e7d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -602,6 +1388,9 @@
     <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="31" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="21" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="21" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -617,40 +1406,57 @@
       <x:c r="J1" s="2"/>
       <x:c r="K1" s="2"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="2"/>
       <x:c r="B2" s="3" t="str">
-        <x:v>MCP agents and MCP Workflow</x:v>
+        <x:v>Measured results</x:v>
       </x:c>
       <x:c r="C2" s="2"/>
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
       <x:c r="F2" s="2"/>
-      <x:c r="G2" s="2"/>
-      <x:c r="H2" s="2"/>
-      <x:c r="I2" s="2"/>
+      <x:c r="G2" s="2" t="str">
+        <x:v>Measure</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="str">
+        <x:v>Prompt agent</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="str">
+        <x:v>Saved workflow</x:v>
+      </x:c>
       <x:c r="J2" s="2"/>
       <x:c r="K2" s="2"/>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="2"/>
       <x:c r="B3" s="4" t="str">
-        <x:v>As of October 30, 2026. App v0.16.0. Qualitative comparison, not a matched performance benchmark.</x:v>
-      </x:c>
-      <x:c r="C3" s="2"/>
+        <x:f>TEXT(Benchmark!G5,"0.00")&amp;"x faster"</x:f>
+        <x:v>6.54x faster</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="str">
+        <x:v>Both methods: 100% observed field accuracy.</x:v>
+      </x:c>
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
       <x:c r="F3" s="2"/>
-      <x:c r="G3" s="2"/>
-      <x:c r="H3" s="2"/>
-      <x:c r="I3" s="2"/>
+      <x:c r="G3" s="2" t="str">
+        <x:v>Mean elapsed (s)</x:v>
+      </x:c>
+      <x:c r="H3" s="21" t="n">
+        <x:f>Benchmark!C6</x:f>
+        <x:v>40.048610579999995</x:v>
+      </x:c>
+      <x:c r="I3" s="21" t="n">
+        <x:f>Benchmark!D6</x:f>
+        <x:v>6.123301240000009</x:v>
+      </x:c>
       <x:c r="J3" s="2"/>
       <x:c r="K3" s="2"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2"/>
       <x:c r="B4" s="4" t="str">
-        <x:v>Baseline: an agent given a saved prompt and MCP tools, without a separate saved executable workflow. Agent host features vary.</x:v>
+        <x:v>October 30, 2026. Ten paired local scraper cases. GPT-6.1 Sol, low reasoning. Native workflow needs no per-run model inference.</x:v>
       </x:c>
       <x:c r="C4" s="2"/>
       <x:c r="D4" s="2"/>
@@ -669,9 +1475,15 @@
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
       <x:c r="F5" s="2"/>
-      <x:c r="G5" s="2"/>
-      <x:c r="H5" s="2"/>
-      <x:c r="I5" s="2"/>
+      <x:c r="G5" s="2" t="str">
+        <x:v>Measure</x:v>
+      </x:c>
+      <x:c r="H5" s="2" t="str">
+        <x:v>Prompt agent</x:v>
+      </x:c>
+      <x:c r="I5" s="2" t="str">
+        <x:v>Saved workflow</x:v>
+      </x:c>
       <x:c r="J5" s="2"/>
       <x:c r="K5" s="2"/>
     </x:row>
@@ -690,9 +1502,17 @@
         <x:v>Interpretation</x:v>
       </x:c>
       <x:c r="F6" s="2"/>
-      <x:c r="G6" s="2"/>
-      <x:c r="H6" s="2"/>
-      <x:c r="I6" s="2"/>
+      <x:c r="G6" s="2" t="str">
+        <x:v>Field accuracy</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="n">
+        <x:f>Benchmark!C7</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I6" s="14" t="n">
+        <x:f>Benchmark!D7</x:f>
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="J6" s="2"/>
       <x:c r="K6" s="2"/>
     </x:row>
@@ -723,13 +1543,13 @@
         <x:v>Repeated run speed</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>May plan again on each run. A host can cache or reuse plans.</x:v>
+        <x:v>40.05 s mean with fresh prompt and MCP.</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>Saved graph reuses the plan. Native steps skip model inference.</x:v>
+        <x:v>6.12 s mean with the saved native graph.</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>Expected benefit; not measured.</x:v>
+        <x:v>6.54x faster in this test.</x:v>
       </x:c>
       <x:c r="F8" s="2"/>
       <x:c r="G8" s="2"/>
@@ -765,13 +1585,13 @@
         <x:v>Output accuracy</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>Depends on model, instructions, tools and validation.</x:v>
+        <x:v>100%: 200/200 canonical fields, checked in both CSV and JSON.</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>Native rules repeat configured logic; AI outputs still vary.</x:v>
+        <x:v>100%: 200/200 canonical fields, checked in both CSV and JSON.</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>No comparative accuracy rate yet.</x:v>
+        <x:v>No observed accuracy advantage.</x:v>
       </x:c>
       <x:c r="F10" s="2"/>
       <x:c r="G10" s="2"/>
@@ -786,13 +1606,13 @@
         <x:v>Accuracy when reused</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>A saved prompt repeats intent; the agent may choose a different route.</x:v>
+        <x:v>5/5 changed-input cases correct with the same prompt.</x:v>
       </x:c>
       <x:c r="D11" s="10" t="str">
-        <x:v>Saved steps keep routing and fields. Bad rules repeat errors too.</x:v>
+        <x:v>5/5 changed-input cases correct with the same saved graph.</x:v>
       </x:c>
       <x:c r="E11" s="10" t="str">
-        <x:v>Better control does not prove correctness.</x:v>
+        <x:v>Input values changed; arbitrary page layouts were not tested.</x:v>
       </x:c>
       <x:c r="F11" s="2"/>
       <x:c r="G11" s="2"/>
@@ -975,13 +1795,13 @@
         <x:v>Cost and AI usage</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>Depends on inference calls, tools and subscription/API billing.</x:v>
+        <x:v>153,304.4 reported model tokens/run on average, including cached input.</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>Native steps use no model inference; builder and AI steps do.</x:v>
+        <x:v>0 model tokens per native repeat run. Builder/setup usage excluded.</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>No measured cost saving yet.</x:v>
+        <x:v>No dollar cost comparison. AI steps still consume model tokens.</x:v>
       </x:c>
       <x:c r="F20" s="2"/>
       <x:c r="G20" s="2"/>
@@ -1112,7 +1932,7 @@
     <x:row r="28">
       <x:c r="A28" s="2"/>
       <x:c r="B28" s="2" t="str">
-        <x:v>No prompt-agent baseline or controlled timing sample was collected. Video duration is not workflow execution time.</x:v>
+        <x:v>Matched result: ten trials per method, including six seconds of deliberate waits. One pilot was excluded on both sides.</x:v>
       </x:c>
       <x:c r="C28" s="2"/>
       <x:c r="D28" s="2"/>
@@ -1279,9 +2099,15 @@
       <x:c r="D39" s="2"/>
       <x:c r="E39" s="2"/>
       <x:c r="F39" s="2"/>
-      <x:c r="G39" s="2"/>
-      <x:c r="H39" s="2"/>
-      <x:c r="I39" s="2"/>
+      <x:c r="G39" s="2" t="str">
+        <x:v>Measure</x:v>
+      </x:c>
+      <x:c r="H39" s="2" t="str">
+        <x:v>Prompt agent</x:v>
+      </x:c>
+      <x:c r="I39" s="2" t="str">
+        <x:v>Saved workflow</x:v>
+      </x:c>
       <x:c r="J39" s="2"/>
       <x:c r="K39" s="2"/>
     </x:row>
@@ -1292,9 +2118,17 @@
       <x:c r="D40" s="2"/>
       <x:c r="E40" s="2"/>
       <x:c r="F40" s="2"/>
-      <x:c r="G40" s="2"/>
-      <x:c r="H40" s="2"/>
-      <x:c r="I40" s="2"/>
+      <x:c r="G40" s="2" t="str">
+        <x:v>Mean model tokens/run</x:v>
+      </x:c>
+      <x:c r="H40" s="38" t="n">
+        <x:f>Benchmark!C47</x:f>
+        <x:v>153304.4</x:v>
+      </x:c>
+      <x:c r="I40" s="38" t="n">
+        <x:f>Benchmark!D47</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J40" s="2"/>
       <x:c r="K40" s="2"/>
     </x:row>
@@ -1477,13 +2311,13 @@
     <x:row r="53" ht="46" customHeight="1">
       <x:c r="A53" s="2"/>
       <x:c r="B53" s="9" t="str">
-        <x:v>Interpretation</x:v>
+        <x:v>Measured evidence</x:v>
       </x:c>
       <x:c r="C53" s="9" t="str">
-        <x:v>Speed expectations above are engineering judgments, not benchmark results.</x:v>
+        <x:v>Independent audit, run ledger, files and fixture hashes</x:v>
       </x:c>
       <x:c r="D53" s="9" t="str">
-        <x:v>Use the Benchmark sheet for matched measurements.</x:v>
+        <x:v>benchmarks/results/measured-2026-10-30T08-02-42-177Z</x:v>
       </x:c>
       <x:c r="E53" s="9"/>
       <x:c r="F53" s="2"/>
@@ -1493,12 +2327,18 @@
       <x:c r="J53" s="2"/>
       <x:c r="K53" s="2"/>
     </x:row>
-    <x:row r="54">
+    <x:row r="54" ht="46" customHeight="1">
       <x:c r="A54" s="2"/>
-      <x:c r="B54" s="2"/>
-      <x:c r="C54" s="2"/>
-      <x:c r="D54" s="2"/>
-      <x:c r="E54" s="2"/>
+      <x:c r="B54" s="9" t="str">
+        <x:v>Limits</x:v>
+      </x:c>
+      <x:c r="C54" s="9" t="str">
+        <x:v>Headless native scraping only; excludes UI, setup authoring and AI-heavy workflows.</x:v>
+      </x:c>
+      <x:c r="D54" s="9" t="str">
+        <x:v>An agent reusing code or a higher-level tool is a different baseline.</x:v>
+      </x:c>
+      <x:c r="E54" s="9"/>
       <x:c r="F54" s="2"/>
       <x:c r="G54" s="2"/>
       <x:c r="H54" s="2"/>
@@ -1586,7 +2426,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6bcdfb3d8e54418"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4439c56654474dab"/>
 </x:worksheet>
 </file>
 
@@ -1606,6 +2446,10 @@
     <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="19" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="19" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="21" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="21" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="21" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="21" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1624,7 +2468,7 @@
     <x:row r="2">
       <x:c r="A2" s="2"/>
       <x:c r="B2" s="3" t="str">
-        <x:v>Matched benchmark worksheet</x:v>
+        <x:v>Measured scraper benchmark</x:v>
       </x:c>
       <x:c r="C2" s="2"/>
       <x:c r="D2" s="2"/>
@@ -1639,7 +2483,7 @@
     <x:row r="3">
       <x:c r="A3" s="2"/>
       <x:c r="B3" s="2" t="str">
-        <x:v>No results entered. Yellow cells are measurement inputs. Blank is unknown, not zero.</x:v>
+        <x:v>20 completed runs on October 30, 2026. Raw measurements below; formulas calculate the comparison above.</x:v>
       </x:c>
       <x:c r="C3" s="2"/>
       <x:c r="D3" s="2"/>
@@ -1679,8 +2523,9 @@
       <x:c r="F5" s="2" t="str">
         <x:v>Measured speedup</x:v>
       </x:c>
-      <x:c r="G5" s="15" t="str">
+      <x:c r="G5" s="15" t="n">
         <x:f>IF(OR(C6="",D6="",D6=0),"",C6/D6)</x:f>
+        <x:v>6.540362626353483</x:v>
       </x:c>
       <x:c r="H5" s="2"/>
       <x:c r="I5" s="2"/>
@@ -1692,11 +2537,13 @@
       <x:c r="B6" s="2" t="str">
         <x:v>Average elapsed time (s)</x:v>
       </x:c>
-      <x:c r="C6" s="13" t="str">
+      <x:c r="C6" s="21" t="n">
         <x:f>IF(COUNTIFS($B$15:$B$34,C$5,$D$15:$D$34,"&lt;&gt;",$D$15:$D$34,"&gt;=0")=0,"",SUMIFS($D$15:$D$34,$B$15:$B$34,C$5)/COUNTIFS($B$15:$B$34,C$5,$D$15:$D$34,"&lt;&gt;",$D$15:$D$34,"&gt;=0"))</x:f>
-      </x:c>
-      <x:c r="D6" s="13" t="str">
+        <x:v>40.048610579999995</x:v>
+      </x:c>
+      <x:c r="D6" s="21" t="n">
         <x:f>IF(COUNTIFS($B$15:$B$34,D$5,$D$15:$D$34,"&lt;&gt;",$D$15:$D$34,"&gt;=0")=0,"",SUMIFS($D$15:$D$34,$B$15:$B$34,D$5)/COUNTIFS($B$15:$B$34,D$5,$D$15:$D$34,"&lt;&gt;",$D$15:$D$34,"&gt;=0"))</x:f>
+        <x:v>6.123301240000009</x:v>
       </x:c>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2"/>
@@ -1711,18 +2558,21 @@
       <x:c r="B7" s="2" t="str">
         <x:v>Field accuracy</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="str">
+      <x:c r="C7" s="14" t="n">
         <x:f>IF(SUMIFS($F$15:$F$34,$B$15:$B$34,C$5)=0,"",SUMIFS($E$15:$E$34,$B$15:$B$34,C$5)/SUMIFS($F$15:$F$34,$B$15:$B$34,C$5))</x:f>
-      </x:c>
-      <x:c r="D7" s="14" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="n">
         <x:f>IF(SUMIFS($F$15:$F$34,$B$15:$B$34,D$5)=0,"",SUMIFS($E$15:$E$34,$B$15:$B$34,D$5)/SUMIFS($F$15:$F$34,$B$15:$B$34,D$5))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2" t="str">
         <x:v>Accuracy delta (pp)</x:v>
       </x:c>
-      <x:c r="G7" s="13" t="str">
+      <x:c r="G7" s="13" t="n">
         <x:f>IF(OR(C7="",D7=""),"",(D7-C7)*100)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="2"/>
       <x:c r="I7" s="2"/>
@@ -1734,11 +2584,13 @@
       <x:c r="B8" s="2" t="str">
         <x:v>Successful run rate</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="str">
+      <x:c r="C8" s="14" t="n">
         <x:f>IF(COUNTIFS($B$15:$B$34,C$5,$G$15:$G$34,"&lt;&gt;",$G$15:$G$34,"&gt;=0")=0,"",SUMIFS($G$15:$G$34,$B$15:$B$34,C$5)/COUNTIFS($B$15:$B$34,C$5,$G$15:$G$34,"&lt;&gt;",$G$15:$G$34,"&gt;=0"))</x:f>
-      </x:c>
-      <x:c r="D8" s="14" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="n">
         <x:f>IF(COUNTIFS($B$15:$B$34,D$5,$G$15:$G$34,"&lt;&gt;",$G$15:$G$34,"&gt;=0")=0,"",SUMIFS($G$15:$G$34,$B$15:$B$34,D$5)/COUNTIFS($B$15:$B$34,D$5,$G$15:$G$34,"&lt;&gt;",$G$15:$G$34,"&gt;=0"))</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2"/>
@@ -1753,11 +2605,13 @@
       <x:c r="B9" s="2" t="str">
         <x:v>Average human fixes</x:v>
       </x:c>
-      <x:c r="C9" s="13" t="str">
+      <x:c r="C9" s="13" t="n">
         <x:f>IF(COUNTIFS($B$15:$B$34,C$5,$H$15:$H$34,"&lt;&gt;",$H$15:$H$34,"&gt;=0")=0,"",SUMIFS($H$15:$H$34,$B$15:$B$34,C$5)/COUNTIFS($B$15:$B$34,C$5,$H$15:$H$34,"&lt;&gt;",$H$15:$H$34,"&gt;=0"))</x:f>
-      </x:c>
-      <x:c r="D9" s="13" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="n">
         <x:f>IF(COUNTIFS($B$15:$B$34,D$5,$H$15:$H$34,"&lt;&gt;",$H$15:$H$34,"&gt;=0")=0,"",SUMIFS($H$15:$H$34,$B$15:$B$34,D$5)/COUNTIFS($B$15:$B$34,D$5,$H$15:$H$34,"&lt;&gt;",$H$15:$H$34,"&gt;=0"))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
@@ -1769,9 +2623,17 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="2"/>
-      <x:c r="B10" s="2"/>
-      <x:c r="C10" s="2"/>
-      <x:c r="D10" s="2"/>
+      <x:c r="B10" s="2" t="str">
+        <x:v>Median elapsed time (s)</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="n">
+        <x:f>MEDIAN(D15,D17,D19,D21,D23,D25,D27,D29,D31,D33)</x:f>
+        <x:v>39.513275300000004</x:v>
+      </x:c>
+      <x:c r="D10" s="21" t="n">
+        <x:f>MEDIAN(D16,D18,D20,D22,D24,D26,D28,D30,D32,D34)</x:f>
+        <x:v>6.122887000000002</x:v>
+      </x:c>
       <x:c r="E10" s="2"/>
       <x:c r="F10" s="2"/>
       <x:c r="G10" s="2"/>
@@ -1783,10 +2645,16 @@
     <x:row r="11">
       <x:c r="A11" s="2"/>
       <x:c r="B11" s="2" t="str">
-        <x:v>Use the same model/version, tools, frozen inputs, expected fields, timeout and task. Alternate methods across 10 paired runs.</x:v>
-      </x:c>
-      <x:c r="C11" s="2"/>
-      <x:c r="D11" s="2"/>
+        <x:v>Minimum elapsed time (s)</x:v>
+      </x:c>
+      <x:c r="C11" s="21" t="n">
+        <x:f>MIN(D15,D17,D19,D21,D23,D25,D27,D29,D31,D33)</x:f>
+        <x:v>29.247441099999996</x:v>
+      </x:c>
+      <x:c r="D11" s="21" t="n">
+        <x:f>MIN(D16,D18,D20,D22,D24,D26,D28,D30,D32,D34)</x:f>
+        <x:v>6.096144200000002</x:v>
+      </x:c>
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
       <x:c r="G11" s="2"/>
@@ -1798,10 +2666,16 @@
     <x:row r="12">
       <x:c r="A12" s="2"/>
       <x:c r="B12" s="2" t="str">
-        <x:v>Measure setup separately. Time start-to-validated-file, including waits/retries. Keep failed runs and mark success 0.</x:v>
-      </x:c>
-      <x:c r="C12" s="2"/>
-      <x:c r="D12" s="2"/>
+        <x:v>Maximum elapsed time (s)</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="n">
+        <x:f>MAX(D15,D17,D19,D21,D23,D25,D27,D29,D31,D33)</x:f>
+        <x:v>55.79296789999999</x:v>
+      </x:c>
+      <x:c r="D12" s="21" t="n">
+        <x:f>MAX(D16,D18,D20,D22,D24,D26,D28,D30,D32,D34)</x:f>
+        <x:v>6.167543500000029</x:v>
+      </x:c>
       <x:c r="E12" s="2"/>
       <x:c r="F12" s="2"/>
       <x:c r="G12" s="2"/>
@@ -1847,10 +2721,20 @@
         <x:v>Human fixes</x:v>
       </x:c>
       <x:c r="I14" s="8" t="str">
-        <x:v>Tokens (optional)</x:v>
-      </x:c>
-      <x:c r="J14" s="2"/>
-      <x:c r="K14" s="2"/>
+        <x:v>Total model tokens</x:v>
+      </x:c>
+      <x:c r="J14" s="30" t="str">
+        <x:v>Input tokens</x:v>
+      </x:c>
+      <x:c r="K14" s="30" t="str">
+        <x:v>Cached input tokens</x:v>
+      </x:c>
+      <x:c r="L14" s="31" t="str">
+        <x:v>Output tokens</x:v>
+      </x:c>
+      <x:c r="M14" s="31" t="str">
+        <x:v>Reasoning output tokens</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="25" customHeight="1">
       <x:c r="A15" s="2"/>
@@ -1860,14 +2744,36 @@
       <x:c r="C15" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D15" s="17"/>
-      <x:c r="E15" s="18"/>
-      <x:c r="F15" s="18"/>
-      <x:c r="G15" s="18"/>
-      <x:c r="H15" s="18"/>
-      <x:c r="I15" s="18"/>
-      <x:c r="J15" s="2"/>
-      <x:c r="K15" s="2"/>
+      <x:c r="D15" s="32" t="n">
+        <x:v>42.3280398</x:v>
+      </x:c>
+      <x:c r="E15" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F15" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G15" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H15" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="36" t="n">
+        <x:v>182967</x:v>
+      </x:c>
+      <x:c r="J15" s="36" t="n">
+        <x:v>181332</x:v>
+      </x:c>
+      <x:c r="K15" s="36" t="n">
+        <x:v>143232</x:v>
+      </x:c>
+      <x:c r="L15" s="37" t="n">
+        <x:v>1635</x:v>
+      </x:c>
+      <x:c r="M15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="25" customHeight="1">
       <x:c r="A16" s="2"/>
@@ -1877,14 +2783,36 @@
       <x:c r="C16" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D16" s="17"/>
-      <x:c r="E16" s="18"/>
-      <x:c r="F16" s="18"/>
-      <x:c r="G16" s="18"/>
-      <x:c r="H16" s="18"/>
-      <x:c r="I16" s="18"/>
-      <x:c r="J16" s="2"/>
-      <x:c r="K16" s="2"/>
+      <x:c r="D16" s="32" t="n">
+        <x:v>6.123118199999997</x:v>
+      </x:c>
+      <x:c r="E16" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F16" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G16" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H16" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I16" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J16" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="25" customHeight="1">
       <x:c r="A17" s="2"/>
@@ -1894,14 +2822,36 @@
       <x:c r="C17" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D17" s="17"/>
-      <x:c r="E17" s="18"/>
-      <x:c r="F17" s="18"/>
-      <x:c r="G17" s="18"/>
-      <x:c r="H17" s="18"/>
-      <x:c r="I17" s="18"/>
-      <x:c r="J17" s="2"/>
-      <x:c r="K17" s="2"/>
+      <x:c r="D17" s="32" t="n">
+        <x:v>44.4053048</x:v>
+      </x:c>
+      <x:c r="E17" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F17" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G17" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H17" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" s="36" t="n">
+        <x:v>185533</x:v>
+      </x:c>
+      <x:c r="J17" s="36" t="n">
+        <x:v>183586</x:v>
+      </x:c>
+      <x:c r="K17" s="36" t="n">
+        <x:v>163968</x:v>
+      </x:c>
+      <x:c r="L17" s="37" t="n">
+        <x:v>1947</x:v>
+      </x:c>
+      <x:c r="M17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="25" customHeight="1">
       <x:c r="A18" s="2"/>
@@ -1911,14 +2861,36 @@
       <x:c r="C18" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D18" s="17"/>
-      <x:c r="E18" s="18"/>
-      <x:c r="F18" s="18"/>
-      <x:c r="G18" s="18"/>
-      <x:c r="H18" s="18"/>
-      <x:c r="I18" s="18"/>
-      <x:c r="J18" s="2"/>
-      <x:c r="K18" s="2"/>
+      <x:c r="D18" s="32" t="n">
+        <x:v>6.096144200000002</x:v>
+      </x:c>
+      <x:c r="E18" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F18" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G18" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H18" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="25" customHeight="1">
       <x:c r="A19" s="2"/>
@@ -1928,14 +2900,36 @@
       <x:c r="C19" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D19" s="17"/>
-      <x:c r="E19" s="18"/>
-      <x:c r="F19" s="18"/>
-      <x:c r="G19" s="18"/>
-      <x:c r="H19" s="18"/>
-      <x:c r="I19" s="18"/>
-      <x:c r="J19" s="2"/>
-      <x:c r="K19" s="2"/>
+      <x:c r="D19" s="32" t="n">
+        <x:v>34.024773700000004</x:v>
+      </x:c>
+      <x:c r="E19" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F19" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G19" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H19" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="36" t="n">
+        <x:v>142184</x:v>
+      </x:c>
+      <x:c r="J19" s="36" t="n">
+        <x:v>141586</x:v>
+      </x:c>
+      <x:c r="K19" s="36" t="n">
+        <x:v>122880</x:v>
+      </x:c>
+      <x:c r="L19" s="37" t="n">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="M19" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="25" customHeight="1">
       <x:c r="A20" s="2"/>
@@ -1945,14 +2939,36 @@
       <x:c r="C20" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D20" s="17"/>
-      <x:c r="E20" s="18"/>
-      <x:c r="F20" s="18"/>
-      <x:c r="G20" s="18"/>
-      <x:c r="H20" s="18"/>
-      <x:c r="I20" s="18"/>
-      <x:c r="J20" s="2"/>
-      <x:c r="K20" s="2"/>
+      <x:c r="D20" s="32" t="n">
+        <x:v>6.109858500000002</x:v>
+      </x:c>
+      <x:c r="E20" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F20" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G20" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H20" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I20" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K20" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L20" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="25" customHeight="1">
       <x:c r="A21" s="2"/>
@@ -1962,14 +2978,36 @@
       <x:c r="C21" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D21" s="17"/>
-      <x:c r="E21" s="18"/>
-      <x:c r="F21" s="18"/>
-      <x:c r="G21" s="18"/>
-      <x:c r="H21" s="18"/>
-      <x:c r="I21" s="18"/>
-      <x:c r="J21" s="2"/>
-      <x:c r="K21" s="2"/>
+      <x:c r="D21" s="32" t="n">
+        <x:v>29.247441099999996</x:v>
+      </x:c>
+      <x:c r="E21" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F21" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G21" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H21" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I21" s="36" t="n">
+        <x:v>115581</x:v>
+      </x:c>
+      <x:c r="J21" s="36" t="n">
+        <x:v>114274</x:v>
+      </x:c>
+      <x:c r="K21" s="36" t="n">
+        <x:v>104576</x:v>
+      </x:c>
+      <x:c r="L21" s="37" t="n">
+        <x:v>1307</x:v>
+      </x:c>
+      <x:c r="M21" s="37" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="25" customHeight="1">
       <x:c r="A22" s="2"/>
@@ -1979,14 +3017,36 @@
       <x:c r="C22" s="2" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D22" s="17"/>
-      <x:c r="E22" s="18"/>
-      <x:c r="F22" s="18"/>
-      <x:c r="G22" s="18"/>
-      <x:c r="H22" s="18"/>
-      <x:c r="I22" s="18"/>
-      <x:c r="J22" s="2"/>
-      <x:c r="K22" s="2"/>
+      <x:c r="D22" s="32" t="n">
+        <x:v>6.114583299999999</x:v>
+      </x:c>
+      <x:c r="E22" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F22" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G22" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H22" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J22" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K22" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L22" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M22" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="25" customHeight="1">
       <x:c r="A23" s="2"/>
@@ -1996,14 +3056,36 @@
       <x:c r="C23" s="2" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D23" s="17"/>
-      <x:c r="E23" s="18"/>
-      <x:c r="F23" s="18"/>
-      <x:c r="G23" s="18"/>
-      <x:c r="H23" s="18"/>
-      <x:c r="I23" s="18"/>
-      <x:c r="J23" s="2"/>
-      <x:c r="K23" s="2"/>
+      <x:c r="D23" s="32" t="n">
+        <x:v>37.72880859999999</x:v>
+      </x:c>
+      <x:c r="E23" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F23" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G23" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H23" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I23" s="36" t="n">
+        <x:v>118116</x:v>
+      </x:c>
+      <x:c r="J23" s="36" t="n">
+        <x:v>116178</x:v>
+      </x:c>
+      <x:c r="K23" s="36" t="n">
+        <x:v>83456</x:v>
+      </x:c>
+      <x:c r="L23" s="37" t="n">
+        <x:v>1938</x:v>
+      </x:c>
+      <x:c r="M23" s="37" t="n">
+        <x:v>17</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="25" customHeight="1">
       <x:c r="A24" s="2"/>
@@ -2013,14 +3095,36 @@
       <x:c r="C24" s="2" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D24" s="17"/>
-      <x:c r="E24" s="18"/>
-      <x:c r="F24" s="18"/>
-      <x:c r="G24" s="18"/>
-      <x:c r="H24" s="18"/>
-      <x:c r="I24" s="18"/>
-      <x:c r="J24" s="2"/>
-      <x:c r="K24" s="2"/>
+      <x:c r="D24" s="32" t="n">
+        <x:v>6.111938999999984</x:v>
+      </x:c>
+      <x:c r="E24" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F24" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G24" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H24" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I24" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J24" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K24" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L24" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M24" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="25" customHeight="1">
       <x:c r="A25" s="2"/>
@@ -2030,14 +3134,36 @@
       <x:c r="C25" s="2" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D25" s="17"/>
-      <x:c r="E25" s="18"/>
-      <x:c r="F25" s="18"/>
-      <x:c r="G25" s="18"/>
-      <x:c r="H25" s="18"/>
-      <x:c r="I25" s="18"/>
-      <x:c r="J25" s="2"/>
-      <x:c r="K25" s="2"/>
+      <x:c r="D25" s="32" t="n">
+        <x:v>35.83691159999999</x:v>
+      </x:c>
+      <x:c r="E25" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F25" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G25" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H25" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" s="36" t="n">
+        <x:v>116407</x:v>
+      </x:c>
+      <x:c r="J25" s="36" t="n">
+        <x:v>114822</x:v>
+      </x:c>
+      <x:c r="K25" s="36" t="n">
+        <x:v>82048</x:v>
+      </x:c>
+      <x:c r="L25" s="37" t="n">
+        <x:v>1585</x:v>
+      </x:c>
+      <x:c r="M25" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="25" customHeight="1">
       <x:c r="A26" s="2"/>
@@ -2047,14 +3173,36 @@
       <x:c r="C26" s="2" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D26" s="17"/>
-      <x:c r="E26" s="18"/>
-      <x:c r="F26" s="18"/>
-      <x:c r="G26" s="18"/>
-      <x:c r="H26" s="18"/>
-      <x:c r="I26" s="18"/>
-      <x:c r="J26" s="2"/>
-      <x:c r="K26" s="2"/>
+      <x:c r="D26" s="32" t="n">
+        <x:v>6.128204300000013</x:v>
+      </x:c>
+      <x:c r="E26" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F26" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G26" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H26" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K26" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="25" customHeight="1">
       <x:c r="A27" s="2"/>
@@ -2064,14 +3212,36 @@
       <x:c r="C27" s="2" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D27" s="17"/>
-      <x:c r="E27" s="18"/>
-      <x:c r="F27" s="18"/>
-      <x:c r="G27" s="18"/>
-      <x:c r="H27" s="18"/>
-      <x:c r="I27" s="18"/>
-      <x:c r="J27" s="2"/>
-      <x:c r="K27" s="2"/>
+      <x:c r="D27" s="32" t="n">
+        <x:v>35.66634939999998</x:v>
+      </x:c>
+      <x:c r="E27" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F27" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G27" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="36" t="n">
+        <x:v>118093</x:v>
+      </x:c>
+      <x:c r="J27" s="36" t="n">
+        <x:v>116177</x:v>
+      </x:c>
+      <x:c r="K27" s="36" t="n">
+        <x:v>97408</x:v>
+      </x:c>
+      <x:c r="L27" s="37" t="n">
+        <x:v>1916</x:v>
+      </x:c>
+      <x:c r="M27" s="37" t="n">
+        <x:v>15</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="25" customHeight="1">
       <x:c r="A28" s="2"/>
@@ -2081,14 +3251,36 @@
       <x:c r="C28" s="2" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D28" s="17"/>
-      <x:c r="E28" s="18"/>
-      <x:c r="F28" s="18"/>
-      <x:c r="G28" s="18"/>
-      <x:c r="H28" s="18"/>
-      <x:c r="I28" s="18"/>
-      <x:c r="J28" s="2"/>
-      <x:c r="K28" s="2"/>
+      <x:c r="D28" s="32" t="n">
+        <x:v>6.1226558000000075</x:v>
+      </x:c>
+      <x:c r="E28" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F28" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G28" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K28" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="25" customHeight="1">
       <x:c r="A29" s="2"/>
@@ -2098,14 +3290,36 @@
       <x:c r="C29" s="2" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D29" s="17"/>
-      <x:c r="E29" s="18"/>
-      <x:c r="F29" s="18"/>
-      <x:c r="G29" s="18"/>
-      <x:c r="H29" s="18"/>
-      <x:c r="I29" s="18"/>
-      <x:c r="J29" s="2"/>
-      <x:c r="K29" s="2"/>
+      <x:c r="D29" s="32" t="n">
+        <x:v>44.157766899999984</x:v>
+      </x:c>
+      <x:c r="E29" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F29" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G29" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="36" t="n">
+        <x:v>185326</x:v>
+      </x:c>
+      <x:c r="J29" s="36" t="n">
+        <x:v>183388</x:v>
+      </x:c>
+      <x:c r="K29" s="36" t="n">
+        <x:v>172800</x:v>
+      </x:c>
+      <x:c r="L29" s="37" t="n">
+        <x:v>1938</x:v>
+      </x:c>
+      <x:c r="M29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="25" customHeight="1">
       <x:c r="A30" s="2"/>
@@ -2115,14 +3329,36 @@
       <x:c r="C30" s="2" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D30" s="17"/>
-      <x:c r="E30" s="18"/>
-      <x:c r="F30" s="18"/>
-      <x:c r="G30" s="18"/>
-      <x:c r="H30" s="18"/>
-      <x:c r="I30" s="18"/>
-      <x:c r="J30" s="2"/>
-      <x:c r="K30" s="2"/>
+      <x:c r="D30" s="32" t="n">
+        <x:v>6.1330272000000114</x:v>
+      </x:c>
+      <x:c r="E30" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F30" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G30" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H30" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J30" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K30" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L30" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M30" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="25" customHeight="1">
       <x:c r="A31" s="2"/>
@@ -2132,14 +3368,36 @@
       <x:c r="C31" s="2" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D31" s="17"/>
-      <x:c r="E31" s="18"/>
-      <x:c r="F31" s="18"/>
-      <x:c r="G31" s="18"/>
-      <x:c r="H31" s="18"/>
-      <x:c r="I31" s="18"/>
-      <x:c r="J31" s="2"/>
-      <x:c r="K31" s="2"/>
+      <x:c r="D31" s="32" t="n">
+        <x:v>41.29774200000003</x:v>
+      </x:c>
+      <x:c r="E31" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F31" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G31" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H31" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I31" s="36" t="n">
+        <x:v>183042</x:v>
+      </x:c>
+      <x:c r="J31" s="36" t="n">
+        <x:v>181415</x:v>
+      </x:c>
+      <x:c r="K31" s="36" t="n">
+        <x:v>170880</x:v>
+      </x:c>
+      <x:c r="L31" s="37" t="n">
+        <x:v>1627</x:v>
+      </x:c>
+      <x:c r="M31" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="25" customHeight="1">
       <x:c r="A32" s="2"/>
@@ -2149,14 +3407,36 @@
       <x:c r="C32" s="2" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D32" s="17"/>
-      <x:c r="E32" s="18"/>
-      <x:c r="F32" s="18"/>
-      <x:c r="G32" s="18"/>
-      <x:c r="H32" s="18"/>
-      <x:c r="I32" s="18"/>
-      <x:c r="J32" s="2"/>
-      <x:c r="K32" s="2"/>
+      <x:c r="D32" s="32" t="n">
+        <x:v>6.1259384000000425</x:v>
+      </x:c>
+      <x:c r="E32" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F32" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G32" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H32" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I32" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="25" customHeight="1">
       <x:c r="A33" s="2"/>
@@ -2166,14 +3446,36 @@
       <x:c r="C33" s="2" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D33" s="17"/>
-      <x:c r="E33" s="18"/>
-      <x:c r="F33" s="18"/>
-      <x:c r="G33" s="18"/>
-      <x:c r="H33" s="18"/>
-      <x:c r="I33" s="18"/>
-      <x:c r="J33" s="2"/>
-      <x:c r="K33" s="2"/>
+      <x:c r="D33" s="32" t="n">
+        <x:v>55.79296789999999</x:v>
+      </x:c>
+      <x:c r="E33" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F33" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G33" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H33" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I33" s="36" t="n">
+        <x:v>185795</x:v>
+      </x:c>
+      <x:c r="J33" s="36" t="n">
+        <x:v>183824</x:v>
+      </x:c>
+      <x:c r="K33" s="36" t="n">
+        <x:v>164224</x:v>
+      </x:c>
+      <x:c r="L33" s="37" t="n">
+        <x:v>1971</x:v>
+      </x:c>
+      <x:c r="M33" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="25" customHeight="1">
       <x:c r="A34" s="2"/>
@@ -2183,14 +3485,36 @@
       <x:c r="C34" s="2" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D34" s="17"/>
-      <x:c r="E34" s="18"/>
-      <x:c r="F34" s="18"/>
-      <x:c r="G34" s="18"/>
-      <x:c r="H34" s="18"/>
-      <x:c r="I34" s="18"/>
-      <x:c r="J34" s="2"/>
-      <x:c r="K34" s="2"/>
+      <x:c r="D34" s="32" t="n">
+        <x:v>6.167543500000029</x:v>
+      </x:c>
+      <x:c r="E34" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F34" s="33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G34" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H34" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K34" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="2"/>
@@ -2221,7 +3545,7 @@
     <x:row r="37">
       <x:c r="A37" s="2"/>
       <x:c r="B37" s="2" t="str">
-        <x:v>Field accuracy = correct expected fields / total expected fields. Missing or wrong values are incorrect. Extra rows also fail task success.</x:v>
+        <x:v>Field accuracy counts 20 canonical expected values per trial, validated in BOTH CSV and JSON. Wrong/missing fields are incorrect.</x:v>
       </x:c>
       <x:c r="C37" s="2"/>
       <x:c r="D37" s="2"/>
@@ -2236,7 +3560,7 @@
     <x:row r="38">
       <x:c r="A38" s="2"/>
       <x:c r="B38" s="2" t="str">
-        <x:v>For the scraper, freeze ASIN, title, price and URL for all five unique rows: 20 expected fields per run.</x:v>
+        <x:v>Pairs 1–5: unchanged catalog. 6: price. 7: title. 8: missing optional price. 9: conflicting duplicate. 10: comma and HTML entity.</x:v>
       </x:c>
       <x:c r="C38" s="2"/>
       <x:c r="D38" s="2"/>
@@ -2251,7 +3575,7 @@
     <x:row r="39">
       <x:c r="A39" s="2"/>
       <x:c r="B39" s="2" t="str">
-        <x:v>Success requires the exact expected row set, valid values, the requested file and completion before the shared timeout.</x:v>
+        <x:v>All trials used the same prompt/graph and first-occurrence deduplication. No manual corrections or whole-trial retries.</x:v>
       </x:c>
       <x:c r="C39" s="2"/>
       <x:c r="D39" s="2"/>
@@ -2266,7 +3590,7 @@
     <x:row r="40">
       <x:c r="A40" s="2"/>
       <x:c r="B40" s="2" t="str">
-        <x:v>Speedup = prompt-agent mean time / workflow mean time. Values above 1 favor the workflow. Accuracy difference is workflow minus agent.</x:v>
+        <x:v>Timer includes method startup, both 3-second waits, execution, agent completion and file validation. Compilation/setup authoring excluded.</x:v>
       </x:c>
       <x:c r="C40" s="2"/>
       <x:c r="D40" s="2"/>
@@ -2281,7 +3605,7 @@
     <x:row r="41">
       <x:c r="A41" s="2"/>
       <x:c r="B41" s="2" t="str">
-        <x:v>Enter paired measurements for both methods before using results. Do not compare native scraping with unrelated AI-heavy tasks.</x:v>
+        <x:v>An independent Python CSV/JSON audit reproduced all 20 scores, fixture hashes and aggregate mean/median values.</x:v>
       </x:c>
       <x:c r="C41" s="2"/>
       <x:c r="D41" s="2"/>
@@ -2295,7 +3619,9 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="2"/>
-      <x:c r="B42" s="2"/>
+      <x:c r="B42" s="2" t="str">
+        <x:v>Agent: GPT-6.1 Sol, low reasoning, ChatGPT subscription. Reported tokens include cached input; they are not a dollar cost measure.</x:v>
+      </x:c>
       <x:c r="C42" s="2"/>
       <x:c r="D42" s="2"/>
       <x:c r="E42" s="2"/>
@@ -2308,7 +3634,9 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="2"/>
-      <x:c r="B43" s="2"/>
+      <x:c r="B43" s="2" t="str">
+        <x:v>Workflow: production runGraph/executeNativeStep with native Rust parsing and file writers. Tauri transport replaced by local stdio.</x:v>
+      </x:c>
       <x:c r="C43" s="2"/>
       <x:c r="D43" s="2"/>
       <x:c r="E43" s="2"/>
@@ -2321,7 +3649,9 @@
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="2"/>
-      <x:c r="B44" s="2"/>
+      <x:c r="B44" s="2" t="str">
+        <x:v>These small frozen cases do not establish accuracy on other sites or speed for AI-heavy steps. Shared parser isolates orchestration.</x:v>
+      </x:c>
       <x:c r="C44" s="2"/>
       <x:c r="D44" s="2"/>
       <x:c r="E44" s="2"/>
@@ -2345,11 +3675,17 @@
       <x:c r="J45" s="2"/>
       <x:c r="K45" s="2"/>
     </x:row>
-    <x:row r="46">
+    <x:row r="46" ht="30" customHeight="1">
       <x:c r="A46" s="2"/>
-      <x:c r="B46" s="2"/>
-      <x:c r="C46" s="2"/>
-      <x:c r="D46" s="2"/>
+      <x:c r="B46" s="26" t="str">
+        <x:v>Mean token usage per run</x:v>
+      </x:c>
+      <x:c r="C46" s="26" t="str">
+        <x:v>Prompt agent</x:v>
+      </x:c>
+      <x:c r="D46" s="26" t="str">
+        <x:v>Workflow</x:v>
+      </x:c>
       <x:c r="E46" s="2"/>
       <x:c r="F46" s="2"/>
       <x:c r="G46" s="2"/>
@@ -2360,9 +3696,17 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="2"/>
-      <x:c r="B47" s="2"/>
-      <x:c r="C47" s="2"/>
-      <x:c r="D47" s="2"/>
+      <x:c r="B47" s="2" t="str">
+        <x:v>Total model tokens</x:v>
+      </x:c>
+      <x:c r="C47" s="38" t="n">
+        <x:f>SUMIFS($I$15:$I$34,$B$15:$B$34,C$46)/COUNTIFS($B$15:$B$34,C$46)</x:f>
+        <x:v>153304.4</x:v>
+      </x:c>
+      <x:c r="D47" s="38" t="n">
+        <x:f>SUMIFS($I$15:$I$34,$B$15:$B$34,D$46)/COUNTIFS($B$15:$B$34,D$46)</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E47" s="2"/>
       <x:c r="F47" s="2"/>
       <x:c r="G47" s="2"/>
@@ -2373,9 +3717,17 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="2"/>
-      <x:c r="B48" s="2"/>
-      <x:c r="C48" s="2"/>
-      <x:c r="D48" s="2"/>
+      <x:c r="B48" s="2" t="str">
+        <x:v>Input tokens</x:v>
+      </x:c>
+      <x:c r="C48" s="38" t="n">
+        <x:f>SUMIFS($J$15:$J$34,$B$15:$B$34,C$46)/COUNTIFS($B$15:$B$34,C$46)</x:f>
+        <x:v>151658.2</x:v>
+      </x:c>
+      <x:c r="D48" s="38" t="n">
+        <x:f>SUMIFS($J$15:$J$34,$B$15:$B$34,D$46)/COUNTIFS($B$15:$B$34,D$46)</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E48" s="2"/>
       <x:c r="F48" s="2"/>
       <x:c r="G48" s="2"/>
@@ -2386,9 +3738,17 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="2"/>
-      <x:c r="B49" s="2"/>
-      <x:c r="C49" s="2"/>
-      <x:c r="D49" s="2"/>
+      <x:c r="B49" s="2" t="str">
+        <x:v>Cached input tokens</x:v>
+      </x:c>
+      <x:c r="C49" s="38" t="n">
+        <x:f>SUMIFS($K$15:$K$34,$B$15:$B$34,C$46)/COUNTIFS($B$15:$B$34,C$46)</x:f>
+        <x:v>130547.2</x:v>
+      </x:c>
+      <x:c r="D49" s="38" t="n">
+        <x:f>SUMIFS($K$15:$K$34,$B$15:$B$34,D$46)/COUNTIFS($B$15:$B$34,D$46)</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E49" s="2"/>
       <x:c r="F49" s="2"/>
       <x:c r="G49" s="2"/>
@@ -2399,9 +3759,17 @@
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="2"/>
-      <x:c r="B50" s="2"/>
-      <x:c r="C50" s="2"/>
-      <x:c r="D50" s="2"/>
+      <x:c r="B50" s="2" t="str">
+        <x:v>Output tokens</x:v>
+      </x:c>
+      <x:c r="C50" s="38" t="n">
+        <x:f>SUMIFS($L$15:$L$34,$B$15:$B$34,C$46)/COUNTIFS($B$15:$B$34,C$46)</x:f>
+        <x:v>1646.2</x:v>
+      </x:c>
+      <x:c r="D50" s="38" t="n">
+        <x:f>SUMIFS($L$15:$L$34,$B$15:$B$34,D$46)/COUNTIFS($B$15:$B$34,D$46)</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E50" s="2"/>
       <x:c r="F50" s="2"/>
       <x:c r="G50" s="2"/>
@@ -2412,9 +3780,17 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="2"/>
-      <x:c r="B51" s="2"/>
-      <x:c r="C51" s="2"/>
-      <x:c r="D51" s="2"/>
+      <x:c r="B51" s="2" t="str">
+        <x:v>Reasoning output tokens</x:v>
+      </x:c>
+      <x:c r="C51" s="38" t="n">
+        <x:f>SUMIFS($M$15:$M$34,$B$15:$B$34,C$46)/COUNTIFS($B$15:$B$34,C$46)</x:f>
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="D51" s="38" t="n">
+        <x:f>SUMIFS($M$15:$M$34,$B$15:$B$34,D$46)/COUNTIFS($B$15:$B$34,D$46)</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E51" s="2"/>
       <x:c r="F51" s="2"/>
       <x:c r="G51" s="2"/>
@@ -2438,7 +3814,9 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="2"/>
-      <x:c r="B53" s="2"/>
+      <x:c r="B53" s="2" t="str">
+        <x:v>Tokens are cumulative for the whole agent run. Total = input + output; cached input is included in input and is not added again.</x:v>
+      </x:c>
       <x:c r="C53" s="2"/>
       <x:c r="D53" s="2"/>
       <x:c r="E53" s="2"/>
@@ -2451,7 +3829,9 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="2"/>
-      <x:c r="B54" s="2"/>
+      <x:c r="B54" s="2" t="str">
+        <x:v>Native runs invoke no model. AI builder/setup and AI-heavy steps are excluded; zero here does not mean all workflows use zero tokens.</x:v>
+      </x:c>
       <x:c r="C54" s="2"/>
       <x:c r="D54" s="2"/>
       <x:c r="E54" s="2"/>
